--- a/DataProvider/card_details.xlsx
+++ b/DataProvider/card_details.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="card_details" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -155,7 +155,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.9"/>

--- a/DataProvider/card_details.xlsx
+++ b/DataProvider/card_details.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="card_details" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="64">
   <si>
     <t xml:space="preserve">Transaction Type</t>
   </si>
@@ -47,6 +47,171 @@
   </si>
   <si>
     <t xml:space="preserve">Account Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMV_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000018900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UFAZMJK1ON071341J1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUUVJHWH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMV_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000028900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMV_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000038900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMV_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000058900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMV_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000068900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMV_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000078900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMVCTLS_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000018900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMVCTLS_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000028900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMVCTLS_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000038900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMVCTLS_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000058900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMVCTLS_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000068900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE_EMVCTLS_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02088000078900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIRM_DATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02500b5649534120435245444954950500000480009B02E8009F0607A00000000310109F120b56495341204352454449549F26081A961EC66EB0B1149F2701409F370465C47FA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMV_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1000002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000018900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMV_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000108900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMV_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000038900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMV_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000158900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMV_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000258900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMV_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000358900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMVCTLS_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000018900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMVCTLS_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000108900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMVCTLS_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000038900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMVCTLS_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000158900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMVCTLS_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000258900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC_EMVCTLS_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000358900833493</t>
   </si>
 </sst>
 </file>
@@ -128,12 +293,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -154,10 +323,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.32"/>
@@ -195,246 +364,625 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/card_details.xlsx
+++ b/DataProvider/card_details.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="card_details" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="77">
   <si>
     <t xml:space="preserve">Transaction Type</t>
   </si>
@@ -212,6 +212,45 @@
   </si>
   <si>
     <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02087000358900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMV_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1000003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMV_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMV_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMV_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMV_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMV_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMVCTLS_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMVCTLS_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMVCTLS_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMVCTLS_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMVCTLS_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIZMV2_EMVCTLS_CREDIT_RUPAY</t>
   </si>
 </sst>
 </file>
@@ -323,8 +362,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.9"/>
@@ -984,6 +1023,306 @@
       </c>
       <c r="I26" s="2"/>
     </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="2"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/DataProvider/card_details.xlsx
+++ b/DataProvider/card_details.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="102">
   <si>
     <t xml:space="preserve">Transaction Type</t>
   </si>
@@ -251,6 +251,81 @@
   </si>
   <si>
     <t xml:space="preserve">PRIZMV2_EMVCTLS_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMV_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1000004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000018900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMV_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000028900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMV_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000038900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMV_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000058900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMV_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000068900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMV_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000078900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMVCTLS_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000018900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMVCTLS_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000028900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMVCTLS_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000038900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMVCTLS_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000058900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMVCTLS_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000068900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_EMVCTLS_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02089000078900833493</t>
   </si>
 </sst>
 </file>
@@ -362,8 +437,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
-  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.9"/>
@@ -1323,6 +1398,306 @@
       </c>
       <c r="I38" s="2"/>
     </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>7202020201</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" s="2"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/DataProvider/card_details.xlsx
+++ b/DataProvider/card_details.xlsx
@@ -438,13 +438,15 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I50"/>
-  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="29.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.06"/>
   </cols>
   <sheetData>

--- a/DataProvider/card_details.xlsx
+++ b/DataProvider/card_details.xlsx
@@ -5,14 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="card_details" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="bin_info" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">card_details!$A$1:$E$50</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">card_details!$A$1:$E$68</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="103">
   <si>
     <t xml:space="preserve">Transaction Type</t>
   </si>
@@ -56,156 +56,31 @@
     <t xml:space="preserve">ATOS_TLE_EMV_DEBIT_MASTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE0208</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">555329</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8900833493</t>
-    </r>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553298900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMV_DEBIT_RUPAY</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE0208</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">555323</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8900833493</t>
-    </r>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553238900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMV_CREDIT_VISA</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE0208</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">555324</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8900833493</t>
-    </r>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553248900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMV_CREDIT_MASTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE0208</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">555327</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8900833493</t>
-    </r>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553278900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMV_CREDIT_RUPAY</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE0208</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">555328</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8900833493</t>
-    </r>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553288900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMVCTLS_DEBIT_VISA</t>
@@ -217,156 +92,31 @@
     <t xml:space="preserve">ATOS_TLE_EMVCTLS_DEBIT_MASTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE0208</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">555329</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8900833493</t>
-    </r>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553298900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMVCTLS_DEBIT_RUPAY</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE0208</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">555323</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8900833493</t>
-    </r>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553238900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMVCTLS_CREDIT_VISA</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE0208</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">555324</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8900833493</t>
-    </r>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553248900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMVCTLS_CREDIT_MASTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE0208</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">555327</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8900833493</t>
-    </r>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553278900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMVCTLS_CREDIT_RUPAY</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE0208</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">555328</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8900833493</t>
-    </r>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553288900833493</t>
   </si>
   <si>
     <t xml:space="preserve">HDFC_EMV_DEBIT_VISA</t>
@@ -477,6 +227,84 @@
     <t xml:space="preserve">FDC_EMVCTLS_CREDIT_RUPAY</t>
   </si>
   <si>
+    <t xml:space="preserve">IDFC_EMV_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMV_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMV_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMV_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMV_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553258900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMV_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMVCTLS_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMVCTLS_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMVCTLS_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMVCTLS_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMVCTLS_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553258900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_EMVCTLS_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_MSR_DEBIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010106FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553218900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_MSR_DEBIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010106FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553298900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_MSR_DEBIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010106FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553238900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_MSR_CREDIT_VISA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010106FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553248900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_MSR_CREDIT_MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010106FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553258900833493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDFC_MSR_CREDIT_RUPAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010106FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553288900833493</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONFIRM_DATA</t>
   </si>
   <si>
@@ -498,7 +326,7 @@
     <t xml:space="preserve">DEBIT</t>
   </si>
   <si>
-    <t xml:space="preserve">MASTER</t>
+    <t xml:space="preserve">MASTER_CARD</t>
   </si>
   <si>
     <t xml:space="preserve">RUPAY</t>
@@ -514,7 +342,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -535,11 +363,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -633,8 +456,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E68"/>
+  <sheetFormatPr defaultColWidth="12.2109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="101.89"/>
@@ -1386,11 +1209,281 @@
         <v>67</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="B51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1409,20 +1502,21 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1430,21 +1524,21 @@
         <v>555321</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="n">
         <v>555329</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1452,10 +1546,10 @@
         <v>555323</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1463,21 +1557,21 @@
         <v>555324</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
-        <v>555327</v>
+        <v>555325</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1485,10 +1579,10 @@
         <v>555328</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/DataProvider/card_details.xlsx
+++ b/DataProvider/card_details.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="101">
   <si>
     <t xml:space="preserve">Transaction Type</t>
   </si>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">ATOS_TLE_EMV_CREDIT_MASTER</t>
   </si>
   <si>
-    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553278900833493</t>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553258900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMV_CREDIT_RUPAY</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">ATOS_TLE_EMVCTLS_CREDIT_MASTER</t>
   </si>
   <si>
-    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553278900833493</t>
+    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553258900833493</t>
   </si>
   <si>
     <t xml:space="preserve">ATOS_TLE_EMVCTLS_CREDIT_RUPAY</t>
@@ -242,9 +242,6 @@
     <t xml:space="preserve">IDFC_EMV_CREDIT_MASTER</t>
   </si>
   <si>
-    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010102FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553258900833493</t>
-  </si>
-  <si>
     <t xml:space="preserve">IDFC_EMV_CREDIT_RUPAY</t>
   </si>
   <si>
@@ -261,9 +258,6 @@
   </si>
   <si>
     <t xml:space="preserve">IDFC_EMVCTLS_CREDIT_MASTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FE058A820238008407A0000000041010950508400880009A031810119C01005F2A0203565F3401019F02060000000050009F090200029F10120110A00001220000000000000000000000FF9F1A0203569F1E0836413030343234379F260804E65CB7BC82A8A29F2701809F3303E0F0C89F34031E03009F3501229F360201AF9F37049B5EDF7A9F410400000000FE010191FE0803323036FE0910D2F8EA7E5D3D6BD4B29A659DCC111386FE03021808FE0A08CFBB6490E3F1C351FE0D0AFFFF006A004247000404FE061A4E49524F5348412056202020202020202020202020202020202FFE0428B9FE52C1B0E993629389F863C41DFBDA73F3275B2C03AABCAB5853BBB7AD29A0FB20809ACD8D4259FE02085553258900833493</t>
   </si>
   <si>
     <t xml:space="preserve">IDFC_EMVCTLS_CREDIT_RUPAY</t>
@@ -457,10 +451,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E68"/>
-  <sheetFormatPr defaultColWidth="12.2109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="101.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="127.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.06"/>
@@ -814,7 +808,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>41</v>
       </c>
@@ -904,7 +898,7 @@
       </c>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>47</v>
       </c>
@@ -994,7 +988,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>53</v>
       </c>
@@ -1084,7 +1078,7 @@
       </c>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>59</v>
       </c>
@@ -1174,7 +1168,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>65</v>
       </c>
@@ -1269,7 +1263,7 @@
         <v>71</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>7</v>
@@ -1281,7 +1275,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>18</v>
@@ -1296,7 +1290,7 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>20</v>
@@ -1311,7 +1305,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>22</v>
@@ -1326,7 +1320,7 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>24</v>
@@ -1341,7 +1335,7 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>26</v>
@@ -1356,10 +1350,10 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>7</v>
@@ -1371,7 +1365,7 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>30</v>
@@ -1386,10 +1380,10 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>7</v>
@@ -1401,10 +1395,10 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>7</v>
@@ -1416,10 +1410,10 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>7</v>
@@ -1431,10 +1425,10 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>7</v>
@@ -1446,10 +1440,10 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>7</v>
@@ -1461,10 +1455,10 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>7</v>
@@ -1476,10 +1470,10 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -1502,7 +1496,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
@@ -1510,13 +1504,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1524,10 +1518,10 @@
         <v>555321</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1535,10 +1529,10 @@
         <v>555329</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1546,10 +1540,10 @@
         <v>555323</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1557,10 +1551,10 @@
         <v>555324</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1568,10 +1562,10 @@
         <v>555325</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1579,10 +1573,10 @@
         <v>555328</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/DataProvider/card_details.xlsx
+++ b/DataProvider/card_details.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="card_details" sheetId="1" state="visible" r:id="rId2"/>
@@ -451,7 +451,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E68"/>
-  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="127.46"/>
@@ -1496,7 +1496,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
